--- a/artfynd/A 3731-2025 artfynd.xlsx
+++ b/artfynd/A 3731-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,132 +1131,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>90537714</v>
-      </c>
-      <c r="B6" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>219955</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Slåttergubbe</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Slätetorp, söder om, Nrk</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>510174.9473819244</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6535708.760749992</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Lerbäck</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>T-Ask-0995</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>1980-07-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1980-07-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Gunnar Hallin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3731-2025 artfynd.xlsx
+++ b/artfynd/A 3731-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>57033779</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510175.4640690341</v>
+        <v>510175</v>
       </c>
       <c r="R2" t="n">
-        <v>6535708.762116894</v>
+        <v>6535709</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1980-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62085955</v>
+        <v>62085954</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slätetorp 7850/3850, Nrk</t>
+          <t>Slätetorp 7750/3850, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510175.4640690341</v>
+        <v>510177</v>
       </c>
       <c r="R3" t="n">
-        <v>6535708.762116894</v>
+        <v>6535609</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1980-07-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1980-07-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-06-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +853,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Hage</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62085954</v>
+        <v>62085955</v>
       </c>
       <c r="B4" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,14 +905,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slätetorp 7750/3850, Nrk</t>
+          <t>Slätetorp 7850/3850, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510176.7621837073</v>
+        <v>510175</v>
       </c>
       <c r="R4" t="n">
-        <v>6535608.705540176</v>
+        <v>6535709</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -969,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1985-06-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1985-06-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,11 +955,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hage</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,12 +974,7 @@
         <v>62431655</v>
       </c>
       <c r="B5" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510176.7621837073</v>
+        <v>510177</v>
       </c>
       <c r="R5" t="n">
-        <v>6535608.705540176</v>
+        <v>6535609</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1089,19 +1039,9 @@
           <t>1985-06-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1985-06-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3731-2025 artfynd.xlsx
+++ b/artfynd/A 3731-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57033779</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62085954</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62085955</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>